--- a/Data/2025_upperhouse_election_constituency_system_cleaning.xlsx
+++ b/Data/2025_upperhouse_election_constituency_system_cleaning.xlsx
@@ -37,10 +37,10 @@
     <t>衆参すべての当選回数</t>
   </si>
   <si>
-    <t>参議院の当選回数</t>
-  </si>
-  <si>
-    <t>衆議院の当選回数</t>
+    <t>参議院当選回数</t>
+  </si>
+  <si>
+    <t>衆議院当選回数</t>
   </si>
   <si>
     <t>都道府県</t>
@@ -61,10 +61,10 @@
     <t>出生地外立候補フラグ</t>
   </si>
   <si>
-    <t>秘書経験の有無(0が秘書経験あり、1が秘書経験なし)</t>
-  </si>
-  <si>
-    <t>地方議会経験の有無(0が地方議会経験あり、1が地方議会経験なし)</t>
+    <t>秘書経験フラグ</t>
+  </si>
+  <si>
+    <t>地方議会経験フラグ</t>
   </si>
   <si>
     <t>職業(分類)</t>
@@ -1489,7 +1489,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1553,10 +1553,10 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1886,11 +1886,11 @@
     <col min="14" max="14" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="7" width="27.290714285714284" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>

--- a/Data/2025_upperhouse_election_constituency_system_cleaning.xlsx
+++ b/Data/2025_upperhouse_election_constituency_system_cleaning.xlsx
@@ -1479,7 +1479,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1490,12 +1490,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1542,7 +1536,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1554,9 +1548,6 @@
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1870,24 +1861,24 @@
   <dimension ref="A1:R351"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="7" width="27.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="6" width="27.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
@@ -2764,7 +2755,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="5"/>
+      <c r="N16" s="4"/>
       <c r="O16" s="4">
         <v>1</v>
       </c>
@@ -2873,7 +2864,7 @@
       <c r="N18" s="4">
         <v>1</v>
       </c>
-      <c r="O18" s="5"/>
+      <c r="O18" s="4"/>
       <c r="P18" s="4">
         <v>1</v>
       </c>
@@ -2927,7 +2918,7 @@
       <c r="N19" s="4">
         <v>3</v>
       </c>
-      <c r="O19" s="5"/>
+      <c r="O19" s="4"/>
       <c r="P19" s="4">
         <v>1</v>
       </c>
@@ -3149,7 +3140,7 @@
       <c r="N23" s="4">
         <v>2</v>
       </c>
-      <c r="O23" s="5"/>
+      <c r="O23" s="4"/>
       <c r="P23" s="4">
         <v>1</v>
       </c>
@@ -3203,7 +3194,7 @@
       <c r="N24" s="4">
         <v>1</v>
       </c>
-      <c r="O24" s="5"/>
+      <c r="O24" s="4"/>
       <c r="P24" s="4">
         <v>1</v>
       </c>
@@ -3257,7 +3248,7 @@
       <c r="N25" s="4">
         <v>4</v>
       </c>
-      <c r="O25" s="5"/>
+      <c r="O25" s="4"/>
       <c r="P25" s="4">
         <v>1</v>
       </c>
@@ -3367,7 +3358,7 @@
       <c r="N27" s="4">
         <v>3</v>
       </c>
-      <c r="O27" s="5"/>
+      <c r="O27" s="4"/>
       <c r="P27" s="4">
         <v>1</v>
       </c>
@@ -3589,7 +3580,7 @@
       <c r="N31" s="4">
         <v>5</v>
       </c>
-      <c r="O31" s="5"/>
+      <c r="O31" s="4"/>
       <c r="P31" s="4">
         <v>1</v>
       </c>
@@ -3643,7 +3634,7 @@
       <c r="N32" s="4">
         <v>3</v>
       </c>
-      <c r="O32" s="5"/>
+      <c r="O32" s="4"/>
       <c r="P32" s="4">
         <v>1</v>
       </c>
@@ -3688,7 +3679,7 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
-      <c r="N33" s="5"/>
+      <c r="N33" s="4"/>
       <c r="O33" s="4">
         <v>1</v>
       </c>
@@ -3857,7 +3848,7 @@
       <c r="N36" s="4">
         <v>2</v>
       </c>
-      <c r="O36" s="5"/>
+      <c r="O36" s="4"/>
       <c r="P36" s="4">
         <v>1</v>
       </c>
@@ -3967,7 +3958,7 @@
       <c r="N38" s="4">
         <v>3</v>
       </c>
-      <c r="O38" s="5"/>
+      <c r="O38" s="4"/>
       <c r="P38" s="4">
         <v>1</v>
       </c>
@@ -4075,7 +4066,7 @@
       <c r="N40" s="4">
         <v>3</v>
       </c>
-      <c r="O40" s="5"/>
+      <c r="O40" s="4"/>
       <c r="P40" s="4">
         <v>1</v>
       </c>
@@ -4185,7 +4176,7 @@
       <c r="N42" s="4">
         <v>5</v>
       </c>
-      <c r="O42" s="5"/>
+      <c r="O42" s="4"/>
       <c r="P42" s="4">
         <v>1</v>
       </c>
@@ -4239,7 +4230,7 @@
       <c r="N43" s="4">
         <v>3</v>
       </c>
-      <c r="O43" s="5"/>
+      <c r="O43" s="4"/>
       <c r="P43" s="4">
         <v>1</v>
       </c>
@@ -4461,7 +4452,7 @@
       <c r="N47" s="4">
         <v>5</v>
       </c>
-      <c r="O47" s="5"/>
+      <c r="O47" s="4"/>
       <c r="P47" s="4">
         <v>1</v>
       </c>
@@ -4627,7 +4618,7 @@
       <c r="N50" s="4">
         <v>2</v>
       </c>
-      <c r="O50" s="5"/>
+      <c r="O50" s="4"/>
       <c r="P50" s="4">
         <v>0</v>
       </c>
@@ -5073,7 +5064,7 @@
       <c r="N58" s="4">
         <v>1</v>
       </c>
-      <c r="O58" s="5"/>
+      <c r="O58" s="4"/>
       <c r="P58" s="4">
         <v>1</v>
       </c>
@@ -5125,7 +5116,7 @@
       <c r="N59" s="4">
         <v>1</v>
       </c>
-      <c r="O59" s="5"/>
+      <c r="O59" s="4"/>
       <c r="P59" s="4">
         <v>1</v>
       </c>
@@ -5235,7 +5226,7 @@
       <c r="N61" s="4">
         <v>4</v>
       </c>
-      <c r="O61" s="5"/>
+      <c r="O61" s="4"/>
       <c r="P61" s="4">
         <v>1</v>
       </c>
@@ -5345,7 +5336,7 @@
       <c r="N63" s="4">
         <v>3</v>
       </c>
-      <c r="O63" s="5"/>
+      <c r="O63" s="4"/>
       <c r="P63" s="4">
         <v>1</v>
       </c>
@@ -5399,7 +5390,7 @@
       <c r="N64" s="4">
         <v>3</v>
       </c>
-      <c r="O64" s="5"/>
+      <c r="O64" s="4"/>
       <c r="P64" s="4">
         <v>1</v>
       </c>
@@ -5453,7 +5444,7 @@
       <c r="N65" s="4">
         <v>1</v>
       </c>
-      <c r="O65" s="5"/>
+      <c r="O65" s="4"/>
       <c r="P65" s="4">
         <v>1</v>
       </c>
@@ -5507,7 +5498,7 @@
       <c r="N66" s="4">
         <v>3</v>
       </c>
-      <c r="O66" s="5"/>
+      <c r="O66" s="4"/>
       <c r="P66" s="4">
         <v>0</v>
       </c>
@@ -5561,7 +5552,7 @@
       <c r="N67" s="4">
         <v>2</v>
       </c>
-      <c r="O67" s="5"/>
+      <c r="O67" s="4"/>
       <c r="P67" s="4">
         <v>1</v>
       </c>
@@ -5615,7 +5606,7 @@
       <c r="N68" s="4">
         <v>5</v>
       </c>
-      <c r="O68" s="5"/>
+      <c r="O68" s="4"/>
       <c r="P68" s="4">
         <v>1</v>
       </c>
@@ -5669,7 +5660,7 @@
       <c r="N69" s="4">
         <v>1</v>
       </c>
-      <c r="O69" s="5"/>
+      <c r="O69" s="4"/>
       <c r="P69" s="4">
         <v>1</v>
       </c>
@@ -5723,7 +5714,7 @@
       <c r="N70" s="4">
         <v>2</v>
       </c>
-      <c r="O70" s="5"/>
+      <c r="O70" s="4"/>
       <c r="P70" s="4">
         <v>1</v>
       </c>
@@ -5777,7 +5768,7 @@
       <c r="N71" s="4">
         <v>2</v>
       </c>
-      <c r="O71" s="5"/>
+      <c r="O71" s="4"/>
       <c r="P71" s="4">
         <v>1</v>
       </c>
@@ -5887,7 +5878,7 @@
       <c r="N73" s="4">
         <v>4</v>
       </c>
-      <c r="O73" s="5"/>
+      <c r="O73" s="4"/>
       <c r="P73" s="4">
         <v>1</v>
       </c>
@@ -6165,7 +6156,7 @@
       <c r="N78" s="4">
         <v>1</v>
       </c>
-      <c r="O78" s="5"/>
+      <c r="O78" s="4"/>
       <c r="P78" s="4">
         <v>1</v>
       </c>
@@ -6387,7 +6378,7 @@
       <c r="N82" s="4">
         <v>1</v>
       </c>
-      <c r="O82" s="5"/>
+      <c r="O82" s="4"/>
       <c r="P82" s="4">
         <v>1</v>
       </c>
@@ -6497,7 +6488,7 @@
       <c r="N84" s="4">
         <v>3</v>
       </c>
-      <c r="O84" s="5"/>
+      <c r="O84" s="4"/>
       <c r="P84" s="4">
         <v>1</v>
       </c>
@@ -6831,7 +6822,7 @@
       <c r="N90" s="4">
         <v>2</v>
       </c>
-      <c r="O90" s="5"/>
+      <c r="O90" s="4"/>
       <c r="P90" s="4">
         <v>1</v>
       </c>
@@ -7053,7 +7044,7 @@
       <c r="N94" s="4">
         <v>1</v>
       </c>
-      <c r="O94" s="5"/>
+      <c r="O94" s="4"/>
       <c r="P94" s="4">
         <v>1</v>
       </c>
@@ -7163,7 +7154,7 @@
       <c r="N96" s="4">
         <v>1</v>
       </c>
-      <c r="O96" s="5"/>
+      <c r="O96" s="4"/>
       <c r="P96" s="4">
         <v>1</v>
       </c>
@@ -7609,7 +7600,7 @@
       <c r="N104" s="4">
         <v>3</v>
       </c>
-      <c r="O104" s="5"/>
+      <c r="O104" s="4"/>
       <c r="P104" s="4">
         <v>1</v>
       </c>
@@ -7775,7 +7766,7 @@
       <c r="N107" s="4">
         <v>5</v>
       </c>
-      <c r="O107" s="5"/>
+      <c r="O107" s="4"/>
       <c r="P107" s="4">
         <v>1</v>
       </c>
@@ -7829,7 +7820,7 @@
       <c r="N108" s="4">
         <v>2</v>
       </c>
-      <c r="O108" s="5"/>
+      <c r="O108" s="4"/>
       <c r="P108" s="4">
         <v>1</v>
       </c>
@@ -8100,8 +8091,8 @@
       </c>
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
-      <c r="N113" s="5"/>
-      <c r="O113" s="5"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
       <c r="P113" s="4">
         <v>1</v>
       </c>
@@ -8205,7 +8196,7 @@
       <c r="N115" s="4">
         <v>1</v>
       </c>
-      <c r="O115" s="5"/>
+      <c r="O115" s="4"/>
       <c r="P115" s="4">
         <v>1</v>
       </c>
@@ -8483,7 +8474,7 @@
       <c r="N120" s="4">
         <v>2</v>
       </c>
-      <c r="O120" s="5"/>
+      <c r="O120" s="4"/>
       <c r="P120" s="4">
         <v>1</v>
       </c>
@@ -8584,7 +8575,7 @@
       <c r="K122" s="3"/>
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
-      <c r="N122" s="5"/>
+      <c r="N122" s="4"/>
       <c r="O122" s="4">
         <v>1</v>
       </c>
@@ -8641,7 +8632,7 @@
       <c r="N123" s="4">
         <v>3</v>
       </c>
-      <c r="O123" s="5"/>
+      <c r="O123" s="4"/>
       <c r="P123" s="4">
         <v>0</v>
       </c>
@@ -8864,8 +8855,8 @@
       <c r="O127" s="4">
         <v>1</v>
       </c>
-      <c r="P127" s="5"/>
-      <c r="Q127" s="5"/>
+      <c r="P127" s="4"/>
+      <c r="Q127" s="4"/>
       <c r="R127" s="3" t="s">
         <v>76</v>
       </c>
@@ -8972,8 +8963,8 @@
       <c r="O129" s="4">
         <v>1</v>
       </c>
-      <c r="P129" s="5"/>
-      <c r="Q129" s="5"/>
+      <c r="P129" s="4"/>
+      <c r="Q129" s="4"/>
       <c r="R129" s="3" t="s">
         <v>52</v>
       </c>
@@ -9304,7 +9295,7 @@
       <c r="O135" s="4">
         <v>1</v>
       </c>
-      <c r="P135" s="5"/>
+      <c r="P135" s="4"/>
       <c r="Q135" s="4">
         <v>1</v>
       </c>
@@ -9635,7 +9626,7 @@
       <c r="N141" s="4">
         <v>3</v>
       </c>
-      <c r="O141" s="5"/>
+      <c r="O141" s="4"/>
       <c r="P141" s="4">
         <v>1</v>
       </c>
@@ -9689,7 +9680,7 @@
       <c r="N142" s="4">
         <v>5</v>
       </c>
-      <c r="O142" s="5"/>
+      <c r="O142" s="4"/>
       <c r="P142" s="4">
         <v>1</v>
       </c>
@@ -9914,7 +9905,7 @@
       <c r="O146" s="4">
         <v>1</v>
       </c>
-      <c r="P146" s="5"/>
+      <c r="P146" s="4"/>
       <c r="Q146" s="4">
         <v>1</v>
       </c>
@@ -10124,7 +10115,7 @@
       <c r="K150" s="3"/>
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
-      <c r="N150" s="5"/>
+      <c r="N150" s="4"/>
       <c r="O150" s="4">
         <v>0</v>
       </c>
@@ -10520,7 +10511,7 @@
       <c r="O157" s="4">
         <v>1</v>
       </c>
-      <c r="P157" s="5"/>
+      <c r="P157" s="4"/>
       <c r="Q157" s="4">
         <v>1</v>
       </c>
@@ -11071,7 +11062,7 @@
       <c r="N167" s="4">
         <v>3</v>
       </c>
-      <c r="O167" s="5"/>
+      <c r="O167" s="4"/>
       <c r="P167" s="4">
         <v>1</v>
       </c>
@@ -11794,7 +11785,7 @@
       <c r="M180" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="N180" s="5"/>
+      <c r="N180" s="4"/>
       <c r="O180" s="4">
         <v>0</v>
       </c>
@@ -12299,7 +12290,7 @@
       <c r="N189" s="4">
         <v>3</v>
       </c>
-      <c r="O189" s="5"/>
+      <c r="O189" s="4"/>
       <c r="P189" s="4">
         <v>1</v>
       </c>
@@ -12518,7 +12509,7 @@
       <c r="M193" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="N193" s="5"/>
+      <c r="N193" s="4"/>
       <c r="O193" s="4">
         <v>1</v>
       </c>
@@ -12631,7 +12622,7 @@
       <c r="N195" s="4">
         <v>1</v>
       </c>
-      <c r="O195" s="5"/>
+      <c r="O195" s="4"/>
       <c r="P195" s="4">
         <v>1</v>
       </c>
@@ -12800,7 +12791,7 @@
       <c r="O198" s="4">
         <v>0</v>
       </c>
-      <c r="P198" s="5"/>
+      <c r="P198" s="4"/>
       <c r="Q198" s="4">
         <v>1</v>
       </c>
@@ -12907,7 +12898,7 @@
       <c r="N200" s="4">
         <v>4</v>
       </c>
-      <c r="O200" s="5"/>
+      <c r="O200" s="4"/>
       <c r="P200" s="4">
         <v>1</v>
       </c>
@@ -12961,7 +12952,7 @@
       <c r="N201" s="4">
         <v>1</v>
       </c>
-      <c r="O201" s="5"/>
+      <c r="O201" s="4"/>
       <c r="P201" s="4">
         <v>1</v>
       </c>
@@ -13298,8 +13289,8 @@
       <c r="O207" s="4">
         <v>1</v>
       </c>
-      <c r="P207" s="5"/>
-      <c r="Q207" s="5"/>
+      <c r="P207" s="4"/>
+      <c r="Q207" s="4"/>
       <c r="R207" s="3" t="s">
         <v>69</v>
       </c>
@@ -13394,7 +13385,7 @@
       <c r="K209" s="3"/>
       <c r="L209" s="3"/>
       <c r="M209" s="3"/>
-      <c r="N209" s="5"/>
+      <c r="N209" s="4"/>
       <c r="O209" s="4">
         <v>1</v>
       </c>
@@ -13619,7 +13610,7 @@
       <c r="N213" s="4">
         <v>3</v>
       </c>
-      <c r="O213" s="5"/>
+      <c r="O213" s="4"/>
       <c r="P213" s="4">
         <v>0</v>
       </c>
@@ -14009,7 +14000,7 @@
       <c r="N220" s="4">
         <v>1</v>
       </c>
-      <c r="O220" s="5"/>
+      <c r="O220" s="4"/>
       <c r="P220" s="4">
         <v>1</v>
       </c>
@@ -14063,7 +14054,7 @@
       <c r="N221" s="4">
         <v>1</v>
       </c>
-      <c r="O221" s="5"/>
+      <c r="O221" s="4"/>
       <c r="P221" s="4">
         <v>1</v>
       </c>
@@ -14509,9 +14500,9 @@
       <c r="N229" s="4">
         <v>1</v>
       </c>
-      <c r="O229" s="5"/>
-      <c r="P229" s="5"/>
-      <c r="Q229" s="5"/>
+      <c r="O229" s="4"/>
+      <c r="P229" s="4"/>
+      <c r="Q229" s="4"/>
       <c r="R229" s="3" t="s">
         <v>69</v>
       </c>
@@ -14550,8 +14541,8 @@
       <c r="K230" s="3"/>
       <c r="L230" s="3"/>
       <c r="M230" s="3"/>
-      <c r="N230" s="5"/>
-      <c r="O230" s="5"/>
+      <c r="N230" s="4"/>
+      <c r="O230" s="4"/>
       <c r="P230" s="4">
         <v>1</v>
       </c>
@@ -14708,8 +14699,8 @@
       <c r="K233" s="3"/>
       <c r="L233" s="3"/>
       <c r="M233" s="3"/>
-      <c r="N233" s="5"/>
-      <c r="O233" s="5"/>
+      <c r="N233" s="4"/>
+      <c r="O233" s="4"/>
       <c r="P233" s="4">
         <v>1</v>
       </c>
@@ -14875,7 +14866,7 @@
       <c r="N236" s="4">
         <v>1</v>
       </c>
-      <c r="O236" s="5"/>
+      <c r="O236" s="4"/>
       <c r="P236" s="4">
         <v>1</v>
       </c>
@@ -14985,7 +14976,7 @@
       <c r="N238" s="4">
         <v>3</v>
       </c>
-      <c r="O238" s="5"/>
+      <c r="O238" s="4"/>
       <c r="P238" s="4">
         <v>1</v>
       </c>
@@ -15095,7 +15086,7 @@
       <c r="N240" s="4">
         <v>3</v>
       </c>
-      <c r="O240" s="5"/>
+      <c r="O240" s="4"/>
       <c r="P240" s="4">
         <v>1</v>
       </c>
@@ -15152,8 +15143,8 @@
       <c r="O241" s="4">
         <v>1</v>
       </c>
-      <c r="P241" s="5"/>
-      <c r="Q241" s="5"/>
+      <c r="P241" s="4"/>
+      <c r="Q241" s="4"/>
       <c r="R241" s="3" t="s">
         <v>52</v>
       </c>
@@ -15307,7 +15298,7 @@
       <c r="N244" s="4">
         <v>1</v>
       </c>
-      <c r="O244" s="5"/>
+      <c r="O244" s="4"/>
       <c r="P244" s="4">
         <v>1</v>
       </c>
@@ -15753,9 +15744,9 @@
       <c r="N252" s="4">
         <v>1</v>
       </c>
-      <c r="O252" s="5"/>
-      <c r="P252" s="5"/>
-      <c r="Q252" s="5"/>
+      <c r="O252" s="4"/>
+      <c r="P252" s="4"/>
+      <c r="Q252" s="4"/>
       <c r="R252" s="3" t="s">
         <v>127</v>
       </c>
@@ -15803,7 +15794,7 @@
       <c r="N253" s="4">
         <v>1</v>
       </c>
-      <c r="O253" s="5"/>
+      <c r="O253" s="4"/>
       <c r="P253" s="4">
         <v>0</v>
       </c>
@@ -15857,7 +15848,7 @@
       <c r="N254" s="4">
         <v>5</v>
       </c>
-      <c r="O254" s="5"/>
+      <c r="O254" s="4"/>
       <c r="P254" s="4">
         <v>1</v>
       </c>
@@ -15914,7 +15905,7 @@
       <c r="O255" s="4">
         <v>0</v>
       </c>
-      <c r="P255" s="5"/>
+      <c r="P255" s="4"/>
       <c r="Q255" s="4">
         <v>0</v>
       </c>
@@ -16077,8 +16068,8 @@
       <c r="N258" s="4">
         <v>5</v>
       </c>
-      <c r="O258" s="5"/>
-      <c r="P258" s="5"/>
+      <c r="O258" s="4"/>
+      <c r="P258" s="4"/>
       <c r="Q258" s="4">
         <v>0</v>
       </c>
@@ -16244,7 +16235,7 @@
       <c r="O261" s="4">
         <v>1</v>
       </c>
-      <c r="P261" s="5"/>
+      <c r="P261" s="4"/>
       <c r="Q261" s="4">
         <v>1</v>
       </c>
@@ -16351,7 +16342,7 @@
       <c r="N263" s="4">
         <v>2</v>
       </c>
-      <c r="O263" s="5"/>
+      <c r="O263" s="4"/>
       <c r="P263" s="4">
         <v>1</v>
       </c>
@@ -16408,8 +16399,8 @@
       <c r="O264" s="4">
         <v>1</v>
       </c>
-      <c r="P264" s="5"/>
-      <c r="Q264" s="5"/>
+      <c r="P264" s="4"/>
+      <c r="Q264" s="4"/>
       <c r="R264" s="3" t="s">
         <v>38</v>
       </c>
@@ -16572,7 +16563,7 @@
       <c r="O267" s="4">
         <v>0</v>
       </c>
-      <c r="P267" s="5"/>
+      <c r="P267" s="4"/>
       <c r="Q267" s="4">
         <v>0</v>
       </c>
@@ -16850,8 +16841,8 @@
       <c r="O272" s="4">
         <v>0</v>
       </c>
-      <c r="P272" s="5"/>
-      <c r="Q272" s="5"/>
+      <c r="P272" s="4"/>
+      <c r="Q272" s="4"/>
       <c r="R272" s="3" t="s">
         <v>104</v>
       </c>
@@ -17064,7 +17055,7 @@
       <c r="M276" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N276" s="5"/>
+      <c r="N276" s="4"/>
       <c r="O276" s="4">
         <v>1</v>
       </c>
@@ -17121,7 +17112,7 @@
       <c r="N277" s="4">
         <v>1</v>
       </c>
-      <c r="O277" s="5"/>
+      <c r="O277" s="4"/>
       <c r="P277" s="4">
         <v>0</v>
       </c>
@@ -17234,7 +17225,7 @@
       <c r="O279" s="4">
         <v>1</v>
       </c>
-      <c r="P279" s="5"/>
+      <c r="P279" s="4"/>
       <c r="Q279" s="4">
         <v>1</v>
       </c>
@@ -17341,8 +17332,8 @@
       <c r="N281" s="4">
         <v>2</v>
       </c>
-      <c r="O281" s="5"/>
-      <c r="P281" s="5"/>
+      <c r="O281" s="4"/>
+      <c r="P281" s="4"/>
       <c r="Q281" s="4">
         <v>0</v>
       </c>
@@ -17449,7 +17440,7 @@
       <c r="N283" s="4">
         <v>3</v>
       </c>
-      <c r="O283" s="5"/>
+      <c r="O283" s="4"/>
       <c r="P283" s="4">
         <v>1</v>
       </c>
@@ -17951,7 +17942,7 @@
       <c r="N292" s="4">
         <v>2</v>
       </c>
-      <c r="O292" s="5"/>
+      <c r="O292" s="4"/>
       <c r="P292" s="4">
         <v>1</v>
       </c>
@@ -18058,8 +18049,8 @@
       <c r="M294" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N294" s="5"/>
-      <c r="O294" s="5"/>
+      <c r="N294" s="4"/>
+      <c r="O294" s="4"/>
       <c r="P294" s="4">
         <v>1</v>
       </c>
@@ -18785,7 +18776,7 @@
       <c r="N307" s="4">
         <v>3</v>
       </c>
-      <c r="O307" s="5"/>
+      <c r="O307" s="4"/>
       <c r="P307" s="4">
         <v>1</v>
       </c>
@@ -19171,7 +19162,7 @@
       <c r="N314" s="4">
         <v>1</v>
       </c>
-      <c r="O314" s="5"/>
+      <c r="O314" s="4"/>
       <c r="P314" s="4">
         <v>1</v>
       </c>
@@ -19272,8 +19263,8 @@
       <c r="K316" s="3"/>
       <c r="L316" s="3"/>
       <c r="M316" s="3"/>
-      <c r="N316" s="5"/>
-      <c r="O316" s="5"/>
+      <c r="N316" s="4"/>
+      <c r="O316" s="4"/>
       <c r="P316" s="4">
         <v>1</v>
       </c>
@@ -19442,7 +19433,7 @@
       <c r="O319" s="4">
         <v>0</v>
       </c>
-      <c r="P319" s="5"/>
+      <c r="P319" s="4"/>
       <c r="Q319" s="4">
         <v>0</v>
       </c>
@@ -19496,7 +19487,7 @@
       <c r="O320" s="4">
         <v>0</v>
       </c>
-      <c r="P320" s="5"/>
+      <c r="P320" s="4"/>
       <c r="Q320" s="4">
         <v>1</v>
       </c>
@@ -20434,7 +20425,7 @@
       <c r="K337" s="3"/>
       <c r="L337" s="3"/>
       <c r="M337" s="3"/>
-      <c r="N337" s="5"/>
+      <c r="N337" s="4"/>
       <c r="O337" s="4">
         <v>0</v>
       </c>
